--- a/审核导出/silicone_screen_uv_审核.xlsx
+++ b/审核导出/silicone_screen_uv_审核.xlsx
@@ -541,7 +541,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>中國厂 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南厂 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
+          <t>中國廠 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南廠 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -579,7 +579,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>中國厂 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南厂 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
+          <t>中國廠 / 手落機：50.8 X 127 / 自動機：305 X 483 / 越南廠 / a.ASP-1300 / 最小印張：840*350 / b.ST-1050 / 最小印張：560*350</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="V1" s="3" t="inlineStr">
         <is>
-          <t>立体燙金</t>
+          <t>立體擊凸</t>
         </is>
       </c>
       <c r="W1" s="3" t="inlineStr">
         <is>
-          <t>立體擊凸</t>
+          <t>立體燙金</t>
         </is>
       </c>
       <c r="X1" s="3" t="inlineStr">
@@ -1302,14 +1302,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V2" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W2" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V2" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X2" s="5" t="inlineStr">
@@ -2008,14 +2008,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V4" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W4" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V4" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X4" s="5" t="inlineStr">
@@ -2361,14 +2361,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V5" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W5" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V5" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X5" s="5" t="inlineStr">
@@ -2714,14 +2714,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W6" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V6" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X6" s="5" t="inlineStr">
@@ -3067,14 +3067,14 @@
           <t>X</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="W7" s="6" t="inlineStr">
-        <is>
-          <t>V</t>
+      <c r="V7" s="6" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>X</t>
         </is>
       </c>
       <c r="X7" s="5" t="inlineStr">
